--- a/StructureDefinition-Kopiemottagande-enhet.xlsx
+++ b/StructureDefinition-Kopiemottagande-enhet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Kopiemottagande-enhet.xlsx
+++ b/StructureDefinition-Kopiemottagande-enhet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Kopiemottagande enhet).</t>
+    <t>Den organisatoriska enhet som tar emot en kopia av laboratoriesvaret.  
+Eller ”… av remissvaret”, om detta ska vara generellt. I projektet e-remiss finns ingen kopiemottagare, är det något speciellt för laboratorieremisser? 
+2018-03-14: Vi stryker denna ur begreppsmodellen, svarskopia är inget unikt för labbremisser.
+2018-03-09: Jonas Svanberg:  
+Kopiemottagande enhet  
+Nej, svarskopia är inget unikt för labbremisser. Det är en kvarleva från papperstiden, då det var lätt att ta en kopia (på vad som helst) och skicka till någon annan.  
+Det förekommer säkert hos vissa landsting, men vanligast är nog att det bara finns ett svar.</t>
   </si>
   <si>
     <t>Purpose</t>
